--- a/real_estate_forms/025_rental_property_appraisal_request_form--real_estate_forms.xlsx
+++ b/real_estate_forms/025_rental_property_appraisal_request_form--real_estate_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -769,8 +769,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -798,12 +798,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'1',_'label':_'appraiser_1'}</t>
+          <t>appraiser_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': '1', 'label': 'Appraiser 1'}</t>
+          <t>Appraiser 1</t>
         </is>
       </c>
     </row>
@@ -815,12 +815,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'2',_'label':_'appraiser_2'}</t>
+          <t>appraiser_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': '2', 'label': 'Appraiser 2'}</t>
+          <t>Appraiser 2</t>
         </is>
       </c>
     </row>
@@ -832,12 +832,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'3',_'label':_'appraiser_3'}</t>
+          <t>appraiser_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': '3', 'label': 'Appraiser 3'}</t>
+          <t>Appraiser 3</t>
         </is>
       </c>
     </row>
@@ -849,12 +849,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'1',_'label':_'single_family'}</t>
+          <t>single_family</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': '1', 'label': 'Single Family'}</t>
+          <t>Single Family</t>
         </is>
       </c>
     </row>
@@ -866,12 +866,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'2',_'label':_'condo'}</t>
+          <t>condo</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': '2', 'label': 'Condo'}</t>
+          <t>Condo</t>
         </is>
       </c>
     </row>
@@ -883,12 +883,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'3',_'label':_'townhouse'}</t>
+          <t>townhouse</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': '3', 'label': 'Townhouse'}</t>
+          <t>Townhouse</t>
         </is>
       </c>
     </row>
@@ -900,12 +900,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'1',_'label':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': '1', 'label': 'Active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -917,12 +917,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'2',_'label':_'sold'}</t>
+          <t>sold</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': '2', 'label': 'Sold'}</t>
+          <t>Sold</t>
         </is>
       </c>
     </row>
@@ -934,12 +934,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'3',_'label':_'off_market'}</t>
+          <t>off_market</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': '3', 'label': 'Off Market'}</t>
+          <t>Off Market</t>
         </is>
       </c>
     </row>
